--- a/assumption.xlsx
+++ b/assumption.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jinsupark/jinsu-coding/petrochemical_macc_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422CC02D-1992-D54A-9CD4-BE30CE168924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1455F373-2B5A-8143-99C0-4593C8243B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19880" xr2:uid="{2ACB2DDE-8F24-AB4B-9986-83C4833858B0}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17180" activeTab="1" xr2:uid="{2ACB2DDE-8F24-AB4B-9986-83C4833858B0}"/>
   </bookViews>
   <sheets>
     <sheet name="fuel_price" sheetId="1" r:id="rId1"/>
     <sheet name="tech_cost" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="66">
   <si>
     <t>Hydrogen_H2</t>
   </si>
@@ -229,6 +229,12 @@
   </si>
   <si>
     <t>플라즈마 열분해 방식 전기 크래킹 사례. 작동온도 3000–6000 K, 에틸렌 수율 50–60% 달성. 기존 대비 에너지 소비 ~52% 감소로, 톤당 소비가 약 절반 수준으로 줄어듦.</t>
+  </si>
+  <si>
+    <t>단위</t>
+  </si>
+  <si>
+    <t>수치</t>
   </si>
 </sst>
 </file>
@@ -342,7 +348,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -772,107 +778,107 @@
         <v>2</v>
       </c>
       <c r="B2" s="14">
-        <f>B11/$B$15</f>
+        <f t="shared" ref="B2:AA2" si="0">B11/$B$15</f>
         <v>6.7307511295180715</v>
       </c>
       <c r="C2" s="14">
-        <f>C11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>6.5602649568863685</v>
       </c>
       <c r="D2" s="14">
-        <f>D11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>6.3897787842546654</v>
       </c>
       <c r="E2" s="14">
-        <f>E11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>6.2192926116229623</v>
       </c>
       <c r="F2" s="14">
-        <f>F11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>6.0488055161823757</v>
       </c>
       <c r="G2" s="14">
-        <f>G11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>5.8783193435506735</v>
       </c>
       <c r="H2" s="14">
-        <f>H11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>5.7057319350933149</v>
       </c>
       <c r="I2" s="14">
-        <f>I11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>5.5331445266359554</v>
       </c>
       <c r="J2" s="14">
-        <f>J11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>5.3605571181785967</v>
       </c>
       <c r="K2" s="14">
-        <f>K11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>5.1879697097212381</v>
       </c>
       <c r="L2" s="14">
-        <f>L11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>5.0153823012638794</v>
       </c>
       <c r="M2" s="14">
-        <f>M11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>4.8448961286321754</v>
       </c>
       <c r="N2" s="14">
-        <f>N11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>4.6744099560004724</v>
       </c>
       <c r="O2" s="14">
-        <f>O11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>4.5039228605598867</v>
       </c>
       <c r="P2" s="14">
-        <f>P11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>4.3334366879281827</v>
       </c>
       <c r="Q2" s="14">
-        <f>Q11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>4.1629505152964805</v>
       </c>
       <c r="R2" s="14">
-        <f>R11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>3.992464342664777</v>
       </c>
       <c r="S2" s="14">
-        <f>S11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>3.8219772472241904</v>
       </c>
       <c r="T2" s="14">
-        <f>T11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>3.6514910745924873</v>
       </c>
       <c r="U2" s="14">
-        <f>U11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>3.4810049019607838</v>
       </c>
       <c r="V2" s="14">
-        <f>V11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>3.3105178065201986</v>
       </c>
       <c r="W2" s="14">
-        <f>W11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>3.1736467930545715</v>
       </c>
       <c r="X2" s="14">
-        <f>X11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>3.036774856780061</v>
       </c>
       <c r="Y2" s="14">
-        <f>Y11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>2.8999038433144344</v>
       </c>
       <c r="Z2" s="14">
-        <f>Z11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>2.7630319070399247</v>
       </c>
       <c r="AA2" s="14">
-        <f>AA11/$B$15</f>
+        <f t="shared" si="0"/>
         <v>2.6261599707654146</v>
       </c>
     </row>
@@ -881,107 +887,107 @@
         <v>3</v>
       </c>
       <c r="B3" s="14">
-        <f>B12/$B$16</f>
+        <f t="shared" ref="B3:AA3" si="1">B12/$B$16</f>
         <v>129.28818444452443</v>
       </c>
       <c r="C3" s="14">
-        <f>C12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>134.45971182230542</v>
       </c>
       <c r="D3" s="14">
-        <f>D12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>139.83810029519762</v>
       </c>
       <c r="E3" s="14">
-        <f>E12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>145.43162430700554</v>
       </c>
       <c r="F3" s="14">
-        <f>F12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>151.24888927928578</v>
       </c>
       <c r="G3" s="14">
-        <f>G12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>157.29884485045719</v>
       </c>
       <c r="H3" s="14">
-        <f>H12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>163.59079864447548</v>
       </c>
       <c r="I3" s="14">
-        <f>I12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>170.13443059025451</v>
       </c>
       <c r="J3" s="14">
-        <f>J12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>176.93980781386472</v>
       </c>
       <c r="K3" s="14">
-        <f>K12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>184.01740012641926</v>
       </c>
       <c r="L3" s="14">
-        <f>L12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="M3" s="14">
-        <f>M12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="N3" s="14">
-        <f>N12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="O3" s="14">
-        <f>O12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="P3" s="14">
-        <f>P12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="Q3" s="14">
-        <f>Q12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="R3" s="14">
-        <f>R12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="S3" s="14">
-        <f>S12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="T3" s="14">
-        <f>T12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="U3" s="14">
-        <f>U12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="V3" s="14">
-        <f>V12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="W3" s="14">
-        <f>W12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="X3" s="14">
-        <f>X12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="Y3" s="14">
-        <f>Y12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="Z3" s="14">
-        <f>Z12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
       <c r="AA3" s="14">
-        <f>AA12/$B$16</f>
+        <f t="shared" si="1"/>
         <v>191.37809613147607</v>
       </c>
     </row>
@@ -1080,39 +1086,39 @@
         <v>48764.445599999999</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" ref="D7:L7" si="0">C7*1.04</f>
+        <f t="shared" ref="D7:L7" si="2">C7*1.04</f>
         <v>50715.023423999999</v>
       </c>
       <c r="E7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>52743.624360959999</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>54853.369335398398</v>
       </c>
       <c r="G7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>57047.504108814333</v>
       </c>
       <c r="H7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>59329.404273166911</v>
       </c>
       <c r="I7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>61702.58044409359</v>
       </c>
       <c r="J7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>64170.683661857336</v>
       </c>
       <c r="K7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>66737.511008331625</v>
       </c>
       <c r="L7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>69407.011448664896</v>
       </c>
       <c r="M7" s="2">
@@ -1120,59 +1126,59 @@
         <v>69407.011448664896</v>
       </c>
       <c r="N7" s="2">
-        <f t="shared" ref="N7:AA7" si="1">M7</f>
+        <f t="shared" ref="N7:AA7" si="3">M7</f>
         <v>69407.011448664896</v>
       </c>
       <c r="O7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="P7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="Q7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="R7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="S7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="T7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="U7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="V7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="W7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="X7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="Y7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="Z7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
       <c r="AA7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>69407.011448664896</v>
       </c>
     </row>
@@ -1185,213 +1191,213 @@
     <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.2">
       <c r="B11" s="4">
-        <f>B6/$B$9</f>
+        <f t="shared" ref="B11:AA11" si="4">B6/$B$9</f>
         <v>55.865234375</v>
       </c>
       <c r="C11" s="4">
-        <f>C6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>54.450199142156862</v>
       </c>
       <c r="D11" s="4">
-        <f>D6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>53.035163909313731</v>
       </c>
       <c r="E11" s="4">
-        <f>E6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>51.620128676470593</v>
       </c>
       <c r="F11" s="4">
-        <f>F6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>50.205085784313724</v>
       </c>
       <c r="G11" s="4">
-        <f>G6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>48.790050551470593</v>
       </c>
       <c r="H11" s="4">
-        <f>H6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>47.357575061274517</v>
       </c>
       <c r="I11" s="4">
-        <f>I6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>45.925099571078434</v>
       </c>
       <c r="J11" s="4">
-        <f>J6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>44.492624080882358</v>
       </c>
       <c r="K11" s="4">
-        <f>K6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>43.060148590686282</v>
       </c>
       <c r="L11" s="4">
-        <f>L6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>41.627673100490199</v>
       </c>
       <c r="M11" s="4">
-        <f>M6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>40.212637867647061</v>
       </c>
       <c r="N11" s="4">
-        <f>N6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>38.797602634803923</v>
       </c>
       <c r="O11" s="4">
-        <f>O6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>37.382559742647061</v>
       </c>
       <c r="P11" s="4">
-        <f>P6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>35.967524509803923</v>
       </c>
       <c r="Q11" s="4">
-        <f>Q6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>34.552489276960792</v>
       </c>
       <c r="R11" s="4">
-        <f>R6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>33.137454044117653</v>
       </c>
       <c r="S11" s="4">
-        <f>S6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>31.722411151960785</v>
       </c>
       <c r="T11" s="4">
-        <f>T6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>30.307375919117646</v>
       </c>
       <c r="U11" s="4">
-        <f>U6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>28.892340686274508</v>
       </c>
       <c r="V11" s="4">
-        <f>V6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>27.47729779411765</v>
       </c>
       <c r="W11" s="4">
-        <f>W6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>26.341268382352947</v>
       </c>
       <c r="X11" s="4">
-        <f>X6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>25.20523131127451</v>
       </c>
       <c r="Y11" s="4">
-        <f>Y6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>24.069201899509807</v>
       </c>
       <c r="Z11" s="4">
-        <f>Z6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>22.933164828431376</v>
       </c>
       <c r="AA11" s="4">
-        <f>AA6/$B$9</f>
+        <f t="shared" si="4"/>
         <v>21.797127757352943</v>
       </c>
     </row>
     <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.2">
       <c r="B12" s="4">
-        <f>B7/$B$9</f>
+        <f t="shared" ref="B12:AA12" si="5">B7/$B$9</f>
         <v>35.913671874999999</v>
       </c>
       <c r="C12" s="4">
-        <f>C7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>37.350218750000003</v>
       </c>
       <c r="D12" s="4">
-        <f>D7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>38.844227500000002</v>
       </c>
       <c r="E12" s="4">
-        <f>E7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>40.397996599999999</v>
       </c>
       <c r="F12" s="4">
-        <f>F7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>42.013916464000005</v>
       </c>
       <c r="G12" s="4">
-        <f>G7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>43.694473122559998</v>
       </c>
       <c r="H12" s="4">
-        <f>H7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>45.442252047462404</v>
       </c>
       <c r="I12" s="4">
-        <f>I7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>47.259942129360901</v>
       </c>
       <c r="J12" s="4">
-        <f>J7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>49.150339814535343</v>
       </c>
       <c r="K12" s="4">
-        <f>K7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>51.116353407116748</v>
       </c>
       <c r="L12" s="4">
-        <f>L7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="M12" s="4">
-        <f>M7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="N12" s="4">
-        <f>N7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="O12" s="4">
-        <f>O7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="P12" s="4">
-        <f>P7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="Q12" s="4">
-        <f>Q7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="R12" s="4">
-        <f>R7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="S12" s="4">
-        <f>S7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="T12" s="4">
-        <f>T7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="U12" s="4">
-        <f>U7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="V12" s="4">
-        <f>V7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="W12" s="4">
-        <f>W7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="X12" s="4">
-        <f>X7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="Y12" s="4">
-        <f>Y7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="Z12" s="4">
-        <f>Z7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
       <c r="AA12" s="4">
-        <f>AA7/$B$9</f>
+        <f t="shared" si="5"/>
         <v>53.161007543401425</v>
       </c>
     </row>
@@ -1441,8 +1447,12 @@
       <c r="D1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="E1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>65</v>
+      </c>
       <c r="G1" s="11" t="s">
         <v>7</v>
       </c>
